--- a/airline_G3_ytest.xlsx
+++ b/airline_G3_ytest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>target</t>
         </is>

--- a/airline_G3_ytest.xlsx
+++ b/airline_G3_ytest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +417,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>target</t>
         </is>
@@ -457,7 +445,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -472,7 +460,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +530,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -647,7 +635,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -702,7 +690,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -747,7 +735,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -857,7 +845,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -922,7 +910,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -937,7 +925,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -972,7 +960,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -1177,7 +1165,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -1252,7 +1240,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -1332,7 +1320,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -1372,7 +1360,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -1457,7 +1445,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -1467,7 +1455,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -1502,7 +1490,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -1537,7 +1525,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -1552,7 +1540,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -1577,7 +1565,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -1627,7 +1615,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -1672,7 +1660,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -1747,7 +1735,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -1757,7 +1745,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -1772,12 +1760,12 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -1927,7 +1915,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -1977,7 +1965,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -1997,7 +1985,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
@@ -2007,7 +1995,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -2137,7 +2125,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -2172,7 +2160,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -2187,12 +2175,12 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -2252,7 +2240,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -2287,7 +2275,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -2337,7 +2325,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -2442,7 +2430,7 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404">
@@ -2452,7 +2440,7 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="406">
@@ -2462,7 +2450,7 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408">
@@ -2477,12 +2465,12 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -2537,12 +2525,12 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424">
@@ -2607,7 +2595,7 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -2647,7 +2635,7 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
@@ -2657,7 +2645,7 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447">
@@ -2667,7 +2655,7 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -2757,7 +2745,7 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467">
@@ -2792,7 +2780,7 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
@@ -2917,7 +2905,7 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499">
@@ -2927,7 +2915,7 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501">
@@ -3042,7 +3030,7 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
@@ -3172,7 +3160,7 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="550">
@@ -3207,7 +3195,7 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="557">
@@ -3312,7 +3300,7 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="578">
@@ -3432,7 +3420,7 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="602">
@@ -3592,7 +3580,7 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="634">
@@ -3632,7 +3620,7 @@
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="642">
@@ -3737,7 +3725,7 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="663">
@@ -3747,7 +3735,7 @@
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="665">
@@ -3822,7 +3810,7 @@
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="680">
@@ -3847,7 +3835,7 @@
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="685">
@@ -3892,7 +3880,7 @@
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="694">
@@ -3912,7 +3900,7 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="698">
@@ -3957,7 +3945,7 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="707">
@@ -4032,7 +4020,7 @@
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="722">
@@ -4092,7 +4080,7 @@
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="734">
@@ -4217,7 +4205,7 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="759">
@@ -4242,7 +4230,7 @@
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764">
@@ -4287,7 +4275,7 @@
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="773">
@@ -4362,7 +4350,7 @@
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="788">
@@ -4567,7 +4555,7 @@
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="829">
@@ -4667,12 +4655,12 @@
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="850">
@@ -4837,12 +4825,12 @@
     </row>
     <row r="882">
       <c r="A882" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="884">
@@ -4862,7 +4850,7 @@
     </row>
     <row r="887">
       <c r="A887" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="888">
@@ -4897,7 +4885,7 @@
     </row>
     <row r="894">
       <c r="A894" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="895">
@@ -5067,7 +5055,7 @@
     </row>
     <row r="928">
       <c r="A928" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="929">
@@ -5142,7 +5130,7 @@
     </row>
     <row r="943">
       <c r="A943" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="944">
